--- a/Proyecto_Financiero_Eventos_Actualizado.xlsx
+++ b/Proyecto_Financiero_Eventos_Actualizado.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro de Ingresos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro de Gastos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anexo de recibos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movimientos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Presupuestos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comprobantes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,33 +427,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Notas</t>
         </is>
       </c>
     </row>
@@ -468,38 +493,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>Mes</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Concepto</t>
+          <t>Categoría</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
+          <t>Límite</t>
         </is>
       </c>
     </row>
@@ -530,7 +540,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Tipo (Ingreso/Gasto)</t>
+          <t>Movimiento_ID</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -545,12 +555,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Nombre del archivo o enlace</t>
+          <t>Enlace</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Código QR</t>
+          <t>Tipo</t>
         </is>
       </c>
     </row>
